--- a/marketer_forms/004_music_promotion_form--marketer_forms.xlsx
+++ b/marketer_forms/004_music_promotion_form--marketer_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -734,8 +734,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -763,12 +763,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'interest_1',_'value':_'interest_1'}</t>
+          <t>interest_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Interest 1', 'value': 'interest_1'}</t>
+          <t>Interest 1</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'interest_2',_'value':_'interest_2'}</t>
+          <t>interest_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Interest 2', 'value': 'interest_2'}</t>
+          <t>Interest 2</t>
         </is>
       </c>
     </row>
@@ -797,12 +797,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'interest_3',_'value':_'interest_3'}</t>
+          <t>interest_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Interest 3', 'value': 'interest_3'}</t>
+          <t>Interest 3</t>
         </is>
       </c>
     </row>
@@ -814,12 +814,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'interest_4',_'value':_'interest_4'}</t>
+          <t>interest_4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Interest 4', 'value': 'interest_4'}</t>
+          <t>Interest 4</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'interest_5',_'value':_'interest_5'}</t>
+          <t>interest_5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Interest 5', 'value': 'interest_5'}</t>
+          <t>Interest 5</t>
         </is>
       </c>
     </row>
@@ -848,12 +848,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'interest_6',_'value':_'interest_6'}</t>
+          <t>interest_6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Interest 6', 'value': 'interest_6'}</t>
+          <t>Interest 6</t>
         </is>
       </c>
     </row>
@@ -865,12 +865,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'interest_7',_'value':_'interest_7'}</t>
+          <t>interest_7</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Interest 7', 'value': 'interest_7'}</t>
+          <t>Interest 7</t>
         </is>
       </c>
     </row>
@@ -882,12 +882,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'interest_8',_'value':_'interest_8'}</t>
+          <t>interest_8</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Interest 8', 'value': 'interest_8'}</t>
+          <t>Interest 8</t>
         </is>
       </c>
     </row>
@@ -899,12 +899,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'interest_9',_'value':_'interest_9'}</t>
+          <t>interest_9</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Interest 9', 'value': 'interest_9'}</t>
+          <t>Interest 9</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'interest_10',_'value':_'interest_10'}</t>
+          <t>interest_10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Interest 10', 'value': 'interest_10'}</t>
+          <t>Interest 10</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'interest_11',_'value':_'interest_11'}</t>
+          <t>interest_11</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Interest 11', 'value': 'interest_11'}</t>
+          <t>Interest 11</t>
         </is>
       </c>
     </row>
@@ -950,12 +950,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'interest_12',_'value':_'interest_12'}</t>
+          <t>interest_12</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Interest 12', 'value': 'interest_12'}</t>
+          <t>Interest 12</t>
         </is>
       </c>
     </row>
@@ -967,12 +967,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'interest_13',_'value':_'interest_13'}</t>
+          <t>interest_13</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Interest 13', 'value': 'interest_13'}</t>
+          <t>Interest 13</t>
         </is>
       </c>
     </row>
@@ -984,12 +984,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'interest_14',_'value':_'interest_14'}</t>
+          <t>interest_14</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Interest 14', 'value': 'interest_14'}</t>
+          <t>Interest 14</t>
         </is>
       </c>
     </row>
@@ -1001,12 +1001,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'interest_15',_'value':_'interest_15'}</t>
+          <t>interest_15</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Interest 15', 'value': 'interest_15'}</t>
+          <t>Interest 15</t>
         </is>
       </c>
     </row>
@@ -1018,12 +1018,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'interest_16',_'value':_'interest_16'}</t>
+          <t>interest_16</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Interest 16', 'value': 'interest_16'}</t>
+          <t>Interest 16</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'interest_17',_'value':_'interest_17'}</t>
+          <t>interest_17</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Interest 17', 'value': 'interest_17'}</t>
+          <t>Interest 17</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'interest_18',_'value':_'interest_18'}</t>
+          <t>interest_18</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Interest 18', 'value': 'interest_18'}</t>
+          <t>Interest 18</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'interest_19',_'value':_'interest_19'}</t>
+          <t>interest_19</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Interest 19', 'value': 'interest_19'}</t>
+          <t>Interest 19</t>
         </is>
       </c>
     </row>
@@ -1086,12 +1086,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'interest_20',_'value':_'interest_20'}</t>
+          <t>interest_20</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Interest 20', 'value': 'interest_20'}</t>
+          <t>Interest 20</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'agreement_1',_'value':_'agreement_1'}</t>
+          <t>agreement_1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Agreement 1', 'value': 'agreement_1'}</t>
+          <t>Agreement 1</t>
         </is>
       </c>
     </row>
@@ -1120,12 +1120,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'agreement_2',_'value':_'agreement_2'}</t>
+          <t>agreement_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Agreement 2', 'value': 'agreement_2'}</t>
+          <t>Agreement 2</t>
         </is>
       </c>
     </row>
@@ -1137,12 +1137,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'agreement_3',_'value':_'agreement_3'}</t>
+          <t>agreement_3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Agreement 3', 'value': 'agreement_3'}</t>
+          <t>Agreement 3</t>
         </is>
       </c>
     </row>
@@ -1154,12 +1154,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'agreement_4',_'value':_'agreement_4'}</t>
+          <t>agreement_4</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Agreement 4', 'value': 'agreement_4'}</t>
+          <t>Agreement 4</t>
         </is>
       </c>
     </row>
@@ -1171,12 +1171,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'agreement_5',_'value':_'agreement_5'}</t>
+          <t>agreement_5</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Agreement 5', 'value': 'agreement_5'}</t>
+          <t>Agreement 5</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'agreement_6',_'value':_'agreement_6'}</t>
+          <t>agreement_6</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Agreement 6', 'value': 'agreement_6'}</t>
+          <t>Agreement 6</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'agreement_7',_'value':_'agreement_7'}</t>
+          <t>agreement_7</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Agreement 7', 'value': 'agreement_7'}</t>
+          <t>Agreement 7</t>
         </is>
       </c>
     </row>
@@ -1222,12 +1222,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'agreement_8',_'value':_'agreement_8'}</t>
+          <t>agreement_8</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Agreement 8', 'value': 'agreement_8'}</t>
+          <t>Agreement 8</t>
         </is>
       </c>
     </row>
@@ -1239,12 +1239,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'agreement_9',_'value':_'agreement_9'}</t>
+          <t>agreement_9</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Agreement 9', 'value': 'agreement_9'}</t>
+          <t>Agreement 9</t>
         </is>
       </c>
     </row>
@@ -1256,12 +1256,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'agreement_10',_'value':_'agreement_10'}</t>
+          <t>agreement_10</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Agreement 10', 'value': 'agreement_10'}</t>
+          <t>Agreement 10</t>
         </is>
       </c>
     </row>
